--- a/SAM_Opportunities_Report_20260610_PM.xlsx
+++ b/SAM_Opportunities_Report_20260610_PM.xlsx
@@ -14,10 +14,10 @@
     <sheet name="🔧 Specialty Pipeline" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -849,7 +849,7 @@
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>91</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>91</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N92"/>
+  <dimension ref="B2:N96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1330,7 +1330,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>All open Solicitations sorted by urgency  ·  87 records  ·  As of June 10, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
+          <t>All open Solicitations sorted by urgency  ·  91 records  ·  As of June 10, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="D45" s="38" t="inlineStr">
         <is>
-          <t>AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
+          <t>61--AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
         </is>
       </c>
       <c r="E45" s="20" t="inlineStr">
@@ -5095,194 +5095,194 @@
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
+          <t>FA441826Q0067</t>
+        </is>
+      </c>
+      <c r="D61" s="38" t="inlineStr">
+        <is>
+          <t>841st Network Cabling Installation</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t>North Charleston, South Carolina</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="G61" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H61" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" s="20" t="inlineStr">
+        <is>
+          <t>Jun 26, 2026</t>
+        </is>
+      </c>
+      <c r="J61" s="20" t="inlineStr">
+        <is>
+          <t>15d</t>
+        </is>
+      </c>
+      <c r="K61" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L61" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M61" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N61" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
           <t>140R2026R0007</t>
         </is>
       </c>
-      <c r="D61" s="38" t="inlineStr">
+      <c r="D62" s="30" t="inlineStr">
         <is>
           <t>CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
         </is>
       </c>
-      <c r="E61" s="20" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F61" s="20" t="inlineStr">
+      <c r="F62" s="17" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="G61" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H61" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I61" s="20" t="inlineStr">
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
         <is>
           <t>Jun 27, 2026</t>
         </is>
       </c>
-      <c r="J61" s="20" t="inlineStr">
+      <c r="J62" s="17" t="inlineStr">
         <is>
           <t>16d</t>
         </is>
       </c>
-      <c r="K61" s="41" t="inlineStr">
+      <c r="K62" s="41" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L61" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M61" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N61" s="40" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="B62" s="33" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="C62" s="34" t="inlineStr">
+      <c r="L62" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="B63" s="33" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C63" s="34" t="inlineStr">
         <is>
           <t>W912QR26RA033</t>
         </is>
       </c>
-      <c r="D62" s="25" t="inlineStr">
+      <c r="D63" s="25" t="inlineStr">
         <is>
           <t>Anniston Army Depot (ANAD) Power Generation and Microgrid Project</t>
         </is>
       </c>
-      <c r="E62" s="34" t="inlineStr">
+      <c r="E63" s="34" t="inlineStr">
         <is>
           <t>Anniston, Alabama</t>
         </is>
       </c>
-      <c r="F62" s="34" t="inlineStr">
+      <c r="F63" s="34" t="inlineStr">
         <is>
           <t>237130</t>
         </is>
       </c>
-      <c r="G62" s="35" t="inlineStr">
+      <c r="G63" s="35" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="H62" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" s="34" t="inlineStr">
+      <c r="H63" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="34" t="inlineStr">
         <is>
           <t>Jun 29, 2026</t>
         </is>
       </c>
-      <c r="J62" s="34" t="inlineStr">
+      <c r="J63" s="34" t="inlineStr">
         <is>
           <t>18d</t>
         </is>
       </c>
-      <c r="K62" s="41" t="inlineStr">
+      <c r="K63" s="41" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L62" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M62" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N62" s="37" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="B63" s="20" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="C63" s="20" t="inlineStr">
-        <is>
-          <t>89503426BWA000067</t>
-        </is>
-      </c>
-      <c r="D63" s="38" t="inlineStr">
-        <is>
-          <t>Denison Substation Stage 10, Iowa</t>
-        </is>
-      </c>
-      <c r="E63" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F63" s="20" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="G63" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H63" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="20" t="inlineStr">
-        <is>
-          <t>Jun 29, 2026</t>
-        </is>
-      </c>
-      <c r="J63" s="20" t="inlineStr">
-        <is>
-          <t>18d</t>
-        </is>
-      </c>
-      <c r="K63" s="41" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L63" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M63" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N63" s="40" t="inlineStr">
+      <c r="L63" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" s="37" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -5296,22 +5296,22 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>140P6026B0005</t>
+          <t>89503426BWA000067</t>
         </is>
       </c>
       <c r="D64" s="30" t="inlineStr">
         <is>
-          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
+          <t>Denison Substation Stage 10, Iowa</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>Grand Portage, Minnesota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
@@ -5363,22 +5363,22 @@
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>W912PM26BA001</t>
+          <t>140P6026B0005</t>
         </is>
       </c>
       <c r="D65" s="38" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
+          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Grand Portage, Minnesota</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G65" s="20" t="inlineStr">
@@ -5430,194 +5430,194 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
+          <t>W912PM26BA001</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>Jun 29, 2026</t>
+        </is>
+      </c>
+      <c r="J66" s="17" t="inlineStr">
+        <is>
+          <t>18d</t>
+        </is>
+      </c>
+      <c r="K66" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L66" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="inlineStr">
+        <is>
           <t>W9123826RA016</t>
         </is>
       </c>
-      <c r="D66" s="30" t="inlineStr">
+      <c r="D67" s="38" t="inlineStr">
         <is>
           <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
         </is>
       </c>
-      <c r="E66" s="17" t="inlineStr">
+      <c r="E67" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F66" s="17" t="inlineStr">
+      <c r="F67" s="20" t="inlineStr">
         <is>
           <t>237130</t>
         </is>
       </c>
-      <c r="G66" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H66" s="17" t="inlineStr">
+      <c r="G67" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H67" s="20" t="inlineStr">
         <is>
           <t>$23.0M</t>
         </is>
       </c>
-      <c r="I66" s="17" t="inlineStr">
+      <c r="I67" s="20" t="inlineStr">
         <is>
           <t>Jun 29, 2026</t>
         </is>
       </c>
-      <c r="J66" s="17" t="inlineStr">
+      <c r="J67" s="20" t="inlineStr">
         <is>
           <t>18d</t>
         </is>
       </c>
-      <c r="K66" s="41" t="inlineStr">
+      <c r="K67" s="41" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L66" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="B67" s="33" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C67" s="34" t="inlineStr">
+      <c r="L67" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="B68" s="33" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="C68" s="34" t="inlineStr">
         <is>
           <t>36C10F26B0001</t>
         </is>
       </c>
-      <c r="D67" s="25" t="inlineStr">
+      <c r="D68" s="25" t="inlineStr">
         <is>
           <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
         </is>
       </c>
-      <c r="E67" s="34" t="inlineStr">
+      <c r="E68" s="34" t="inlineStr">
         <is>
           <t>San Antonio, Texas</t>
         </is>
       </c>
-      <c r="F67" s="34" t="inlineStr">
+      <c r="F68" s="34" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="G67" s="35" t="inlineStr">
+      <c r="G68" s="35" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="H67" s="34" t="inlineStr">
+      <c r="H68" s="34" t="inlineStr">
         <is>
           <t>$1.5M</t>
         </is>
       </c>
-      <c r="I67" s="34" t="inlineStr">
+      <c r="I68" s="34" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="J67" s="34" t="inlineStr">
+      <c r="J68" s="34" t="inlineStr">
         <is>
           <t>19d</t>
         </is>
       </c>
-      <c r="K67" s="41" t="inlineStr">
+      <c r="K68" s="41" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L67" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="37" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="C68" s="17" t="inlineStr">
-        <is>
-          <t>W911WN26BA014</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
-        </is>
-      </c>
-      <c r="E68" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F68" s="17" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H68" s="17" t="inlineStr">
-        <is>
-          <t>$45.0M</t>
-        </is>
-      </c>
-      <c r="I68" s="17" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="J68" s="17" t="inlineStr">
-        <is>
-          <t>19d</t>
-        </is>
-      </c>
-      <c r="K68" s="41" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L68" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
+      <c r="L68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="37" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -5631,22 +5631,22 @@
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>12FPC326B0006</t>
+          <t>W911WN26BA014</t>
         </is>
       </c>
       <c r="D69" s="38" t="inlineStr">
         <is>
-          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>Madison, Ohio</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G69" s="20" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="H69" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="I69" s="20" t="inlineStr">
@@ -5698,22 +5698,22 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>FA481426Q0026</t>
+          <t>12FPC326B0006</t>
         </is>
       </c>
       <c r="D70" s="30" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Madison, Ohio</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
@@ -5765,22 +5765,22 @@
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>140P6026B0004</t>
+          <t>140FC226R0002</t>
         </is>
       </c>
       <c r="D71" s="38" t="inlineStr">
         <is>
-          <t>Z--BRVB - Entry Courtyard Improvements</t>
+          <t>MN VLY NWR-HOGBACK LEVEE-FLOOD REPAIR</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>Topeka, Kansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G71" s="20" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="K71" s="41" t="inlineStr">
@@ -5832,22 +5832,22 @@
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0042</t>
+          <t>FA481426Q0026</t>
         </is>
       </c>
       <c r="D72" s="30" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
@@ -5857,17 +5857,17 @@
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="J72" s="17" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="K72" s="41" t="inlineStr">
@@ -5899,22 +5899,22 @@
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>89503326BWA000019</t>
+          <t>140P6026B0004</t>
         </is>
       </c>
       <c r="D73" s="38" t="inlineStr">
         <is>
-          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
+          <t>Z--BRVB - Entry Courtyard Improvements</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Topeka, Kansas</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G73" s="20" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="J73" s="20" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="K73" s="41" t="inlineStr">
@@ -5966,22 +5966,22 @@
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>191BWC26B0001</t>
+          <t>140P8326Q0042</t>
         </is>
       </c>
       <c r="D74" s="30" t="inlineStr">
         <is>
-          <t>Tainter Gates Sandblasting</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>Del Rio, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
@@ -5991,17 +5991,17 @@
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="J74" s="17" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="K74" s="41" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>140FGA26R0021</t>
+          <t>140FC226Q0036</t>
         </is>
       </c>
       <c r="D75" s="38" t="inlineStr">
         <is>
-          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
+          <t>VY-MISSISQUOI NWR-PARKING LOT MAINT</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G75" s="20" t="inlineStr">
@@ -6063,12 +6063,12 @@
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 03, 2026</t>
         </is>
       </c>
       <c r="J75" s="20" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="K75" s="41" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>W9127N26BA015</t>
+          <t>89503326BWA000019</t>
         </is>
       </c>
       <c r="D76" s="30" t="inlineStr">
         <is>
-          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
+          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
@@ -6167,22 +6167,22 @@
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>140P8326Q0041</t>
+          <t>191BWC26B0001</t>
         </is>
       </c>
       <c r="D77" s="38" t="inlineStr">
         <is>
-          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
+          <t>Tainter Gates Sandblasting</t>
         </is>
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Del Rio, Texas</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G77" s="20" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="H77" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="I77" s="20" t="inlineStr">
@@ -6234,17 +6234,17 @@
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>W9127826RA046</t>
+          <t>140FGA26R0021</t>
         </is>
       </c>
       <c r="D78" s="30" t="inlineStr">
         <is>
-          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
+          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>Biloxi, Mississippi</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="I78" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="J78" s="17" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="K78" s="41" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>W912P926BA007</t>
+          <t>W9127N26BA015</t>
         </is>
       </c>
       <c r="D79" s="38" t="inlineStr">
         <is>
-          <t>Crains Island Stage 3</t>
+          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
         </is>
       </c>
       <c r="E79" s="20" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="J79" s="20" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="K79" s="41" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>FA282326R0014</t>
+          <t>140P8326Q0041</t>
         </is>
       </c>
       <c r="D80" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
+          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G80" s="17" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="I80" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="J80" s="17" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="K80" s="41" t="inlineStr">
@@ -6435,22 +6435,22 @@
       </c>
       <c r="C81" s="20" t="inlineStr">
         <is>
-          <t>140P5326R0006</t>
+          <t>W9127826RA046</t>
         </is>
       </c>
       <c r="D81" s="38" t="inlineStr">
         <is>
-          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
+          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
         </is>
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Biloxi, Mississippi</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G81" s="20" t="inlineStr">
@@ -6465,12 +6465,12 @@
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>Jul 08, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="J81" s="20" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="K81" s="41" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>140P6426B0008</t>
+          <t>W912P926BA007</t>
         </is>
       </c>
       <c r="D82" s="30" t="inlineStr">
         <is>
-          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
+          <t>Crains Island Stage 3</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
-          <t>Jul 08, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="J82" s="17" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="K82" s="41" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="C83" s="20" t="inlineStr">
         <is>
-          <t>N6247326R9953</t>
+          <t>FA282326R0014</t>
         </is>
       </c>
       <c r="D83" s="38" t="inlineStr">
         <is>
-          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
+          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
         </is>
       </c>
       <c r="E83" s="20" t="inlineStr">
@@ -6594,17 +6594,17 @@
       </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="K83" s="41" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>140R4026R0010</t>
+          <t>140P5326R0006</t>
         </is>
       </c>
       <c r="D84" s="30" t="inlineStr">
         <is>
-          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
+          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G84" s="17" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 08, 2026</t>
         </is>
       </c>
       <c r="J84" s="17" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="K84" s="41" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="C85" s="20" t="inlineStr">
         <is>
-          <t>N6247326R0053</t>
+          <t>140P6426B0008</t>
         </is>
       </c>
       <c r="D85" s="38" t="inlineStr">
         <is>
-          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
+          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
         </is>
       </c>
       <c r="E85" s="20" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="F85" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G85" s="20" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 08, 2026</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="K85" s="41" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>W9128F26RA056</t>
+          <t>N6247326R9953</t>
         </is>
       </c>
       <c r="D86" s="30" t="inlineStr">
         <is>
-          <t>Solicitation for Grand Forks Fueling System Repairs</t>
+          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>237120</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="G86" s="17" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="C87" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>140R4026R0010</t>
         </is>
       </c>
       <c r="D87" s="38" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
         </is>
       </c>
       <c r="E87" s="20" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G87" s="20" t="inlineStr">
@@ -6867,17 +6867,17 @@
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
         <is>
-          <t>34d</t>
-        </is>
-      </c>
-      <c r="K87" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+          <t>29d</t>
+        </is>
+      </c>
+      <c r="K87" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="L87" s="20" t="inlineStr">
@@ -6897,67 +6897,67 @@
       </c>
     </row>
     <row r="88" ht="32" customHeight="1">
-      <c r="B88" s="33" t="inlineStr">
+      <c r="B88" s="17" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="C88" s="34" t="inlineStr">
-        <is>
-          <t>36C25626R0015</t>
-        </is>
-      </c>
-      <c r="D88" s="25" t="inlineStr">
-        <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
-        </is>
-      </c>
-      <c r="E88" s="34" t="inlineStr">
-        <is>
-          <t>Fayetteville, Arkansas</t>
-        </is>
-      </c>
-      <c r="F88" s="34" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="G88" s="35" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H88" s="34" t="inlineStr">
-        <is>
-          <t>$15.0M</t>
-        </is>
-      </c>
-      <c r="I88" s="34" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="J88" s="34" t="inlineStr">
-        <is>
-          <t>42d</t>
-        </is>
-      </c>
-      <c r="K88" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
-        </is>
-      </c>
-      <c r="L88" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M88" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N88" s="37" t="inlineStr">
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>N6247326R0053</t>
+        </is>
+      </c>
+      <c r="D88" s="30" t="inlineStr">
+        <is>
+          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>Jul 10, 2026</t>
+        </is>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>29d</t>
+        </is>
+      </c>
+      <c r="K88" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M88" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N88" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -6971,22 +6971,22 @@
       </c>
       <c r="C89" s="20" t="inlineStr">
         <is>
-          <t>N6247324R0036</t>
+          <t>W9128F26RA056</t>
         </is>
       </c>
       <c r="D89" s="38" t="inlineStr">
         <is>
-          <t>Marine Corps Base Camp Pendleton (MCBCP) Base Operations Support Contract (BOSC)</t>
+          <t>Solicitation for Grand Forks Fueling System Repairs</t>
         </is>
       </c>
       <c r="E89" s="20" t="inlineStr">
         <is>
-          <t>Oceanside, California</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237120</t>
         </is>
       </c>
       <c r="G89" s="20" t="inlineStr">
@@ -6996,22 +6996,22 @@
       </c>
       <c r="H89" s="20" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="J89" s="20" t="inlineStr">
         <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="K89" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>29d</t>
+        </is>
+      </c>
+      <c r="K89" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="L89" s="20" t="inlineStr">
@@ -7038,22 +7038,22 @@
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>140FC226Q0032</t>
+          <t>12445526Q0044</t>
         </is>
       </c>
       <c r="D90" s="30" t="inlineStr">
         <is>
-          <t>VA-HARRISON LAKE NFH-REPL ELECTRICAL VC</t>
+          <t>GAOA Grand Isle NRA Water System Improvement</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Munising, Michigan</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G90" s="17" t="inlineStr">
@@ -7068,17 +7068,17 @@
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="J90" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="K90" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>29d</t>
+        </is>
+      </c>
+      <c r="K90" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="L90" s="17" t="inlineStr">
@@ -7105,134 +7105,402 @@
       </c>
       <c r="C91" s="20" t="inlineStr">
         <is>
+          <t>140L3626Q0032</t>
+        </is>
+      </c>
+      <c r="D91" s="38" t="inlineStr">
+        <is>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+        </is>
+      </c>
+      <c r="E91" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F91" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G91" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H91" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>Jul 15, 2026</t>
+        </is>
+      </c>
+      <c r="J91" s="20" t="inlineStr">
+        <is>
+          <t>34d</t>
+        </is>
+      </c>
+      <c r="K91" s="42" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
+        </is>
+      </c>
+      <c r="L91" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M91" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N91" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="B92" s="33" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C92" s="34" t="inlineStr">
+        <is>
+          <t>36C25626R0015</t>
+        </is>
+      </c>
+      <c r="D92" s="25" t="inlineStr">
+        <is>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+        </is>
+      </c>
+      <c r="E92" s="34" t="inlineStr">
+        <is>
+          <t>Fayetteville, Arkansas</t>
+        </is>
+      </c>
+      <c r="F92" s="34" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G92" s="35" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H92" s="34" t="inlineStr">
+        <is>
+          <t>$15.0M</t>
+        </is>
+      </c>
+      <c r="I92" s="34" t="inlineStr">
+        <is>
+          <t>Jul 23, 2026</t>
+        </is>
+      </c>
+      <c r="J92" s="34" t="inlineStr">
+        <is>
+          <t>42d</t>
+        </is>
+      </c>
+      <c r="K92" s="42" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
+        </is>
+      </c>
+      <c r="L92" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M92" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N92" s="37" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="32" customHeight="1">
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C93" s="20" t="inlineStr">
+        <is>
+          <t>N6247324R0036</t>
+        </is>
+      </c>
+      <c r="D93" s="38" t="inlineStr">
+        <is>
+          <t>Marine Corps Base Camp Pendleton (MCBCP) Base Operations Support Contract (BOSC)</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>Oceanside, California</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="G93" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H93" s="20" t="inlineStr">
+        <is>
+          <t>$47.0M</t>
+        </is>
+      </c>
+      <c r="I93" s="20" t="inlineStr">
+        <is>
+          <t>Jun 11, 2026</t>
+        </is>
+      </c>
+      <c r="J93" s="20" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="K93" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="L93" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M93" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N93" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>140FC226Q0032</t>
+        </is>
+      </c>
+      <c r="D94" s="30" t="inlineStr">
+        <is>
+          <t>VA-HARRISON LAKE NFH-REPL ELECTRICAL VC</t>
+        </is>
+      </c>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>Jun 11, 2026</t>
+        </is>
+      </c>
+      <c r="J94" s="17" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="K94" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="L94" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M94" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N94" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C95" s="20" t="inlineStr">
+        <is>
           <t>W912DR26QA048</t>
         </is>
       </c>
-      <c r="D91" s="38" t="inlineStr">
+      <c r="D95" s="38" t="inlineStr">
         <is>
           <t>Gravel Road Maintenance</t>
         </is>
       </c>
-      <c r="E91" s="20" t="inlineStr">
+      <c r="E95" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F91" s="20" t="inlineStr">
+      <c r="F95" s="20" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="G91" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H91" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I91" s="20" t="inlineStr">
+      <c r="G95" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H95" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="20" t="inlineStr">
         <is>
           <t>Jun 11, 2026</t>
         </is>
       </c>
-      <c r="J91" s="20" t="inlineStr">
+      <c r="J95" s="20" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="K91" s="18" t="inlineStr">
+      <c r="K95" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L91" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M91" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N91" s="40" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="32" customHeight="1">
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="C92" s="17" t="inlineStr">
+      <c r="L95" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M95" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N95" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="32" customHeight="1">
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
         <is>
           <t>FA446026Q0383</t>
         </is>
       </c>
-      <c r="D92" s="30" t="inlineStr">
+      <c r="D96" s="30" t="inlineStr">
         <is>
           <t>Repair/Replace Traffic Lights</t>
         </is>
       </c>
-      <c r="E92" s="17" t="inlineStr">
+      <c r="E96" s="17" t="inlineStr">
         <is>
           <t>Little Rock Air Force Base, Arkansas</t>
         </is>
       </c>
-      <c r="F92" s="17" t="inlineStr">
+      <c r="F96" s="17" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="G92" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H92" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I92" s="17" t="inlineStr">
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H96" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
         <is>
           <t>Jun 11, 2026</t>
         </is>
       </c>
-      <c r="J92" s="17" t="inlineStr">
+      <c r="J96" s="17" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="K92" s="18" t="inlineStr">
+      <c r="K96" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L92" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M92" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N92" s="32" t="inlineStr">
+      <c r="L96" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M96" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N96" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:N92"/>
+  <autoFilter ref="B5:N96"/>
   <mergeCells count="2">
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B2:N2"/>
@@ -7325,6 +7593,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N90" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N91" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N92" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N93" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N94" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N95" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N96" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7337,7 +7609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K50"/>
+  <dimension ref="B2:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7365,7 +7637,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>Early-stage opportunities to monitor  ·  45 records  (7 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
+          <t>Early-stage opportunities to monitor  ·  46 records  (7 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
         </is>
       </c>
     </row>
@@ -9762,8 +10034,60 @@
         </is>
       </c>
     </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>140P6326B0008</t>
+        </is>
+      </c>
+      <c r="C51" s="38" t="inlineStr">
+        <is>
+          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Medora, North Dakota</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I51" s="20" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J51" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K51" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B5:K50"/>
+  <autoFilter ref="B5:K51"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -9779,7 +10103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K137"/>
+  <dimension ref="B2:K142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9807,7 +10131,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>Complete data  ·  132 records  ·  June 10, 2026</t>
+          <t>Complete data  ·  137 records  ·  June 10, 2026</t>
         </is>
       </c>
     </row>
@@ -11900,7 +12224,7 @@
       </c>
       <c r="C45" s="38" t="inlineStr">
         <is>
-          <t>AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
+          <t>61--AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -12727,154 +13051,154 @@
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="20" t="inlineStr">
         <is>
+          <t>FA441826Q0067</t>
+        </is>
+      </c>
+      <c r="C61" s="38" t="inlineStr">
+        <is>
+          <t>841st Network Cabling Installation</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>North Charleston, South Carolina</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G61" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="20" t="inlineStr">
+        <is>
+          <t>Jun 26, 2026</t>
+        </is>
+      </c>
+      <c r="I61" s="20" t="inlineStr">
+        <is>
+          <t>15d</t>
+        </is>
+      </c>
+      <c r="J61" s="20" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K61" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="B62" s="17" t="inlineStr">
+        <is>
           <t>140R2026R0007</t>
         </is>
       </c>
-      <c r="C61" s="38" t="inlineStr">
+      <c r="C62" s="30" t="inlineStr">
         <is>
           <t>CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
         </is>
       </c>
-      <c r="D61" s="20" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E61" s="20" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F61" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G61" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="20" t="inlineStr">
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
         <is>
           <t>Jun 27, 2026</t>
         </is>
       </c>
-      <c r="I61" s="20" t="inlineStr">
+      <c r="I62" s="17" t="inlineStr">
         <is>
           <t>16d</t>
         </is>
       </c>
-      <c r="J61" s="20" t="inlineStr">
+      <c r="J62" s="17" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K61" s="40" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="B62" s="34" t="inlineStr">
+      <c r="K62" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="B63" s="34" t="inlineStr">
         <is>
           <t>W912QR26RA033</t>
         </is>
       </c>
-      <c r="C62" s="25" t="inlineStr">
+      <c r="C63" s="25" t="inlineStr">
         <is>
           <t>Anniston Army Depot (ANAD) Power Generation and Microgrid Project</t>
         </is>
       </c>
-      <c r="D62" s="34" t="inlineStr">
+      <c r="D63" s="34" t="inlineStr">
         <is>
           <t>Anniston, Alabama</t>
         </is>
       </c>
-      <c r="E62" s="34" t="inlineStr">
+      <c r="E63" s="34" t="inlineStr">
         <is>
           <t>237130</t>
         </is>
       </c>
-      <c r="F62" s="34" t="inlineStr">
+      <c r="F63" s="34" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G62" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="34" t="inlineStr">
+      <c r="G63" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="34" t="inlineStr">
         <is>
           <t>Jun 29, 2026</t>
         </is>
       </c>
-      <c r="I62" s="34" t="inlineStr">
+      <c r="I63" s="34" t="inlineStr">
         <is>
           <t>18d</t>
         </is>
       </c>
-      <c r="J62" s="34" t="inlineStr">
+      <c r="J63" s="34" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K62" s="37" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="B63" s="20" t="inlineStr">
-        <is>
-          <t>89503426BWA000067</t>
-        </is>
-      </c>
-      <c r="C63" s="38" t="inlineStr">
-        <is>
-          <t>Denison Substation Stage 10, Iowa</t>
-        </is>
-      </c>
-      <c r="D63" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E63" s="20" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="F63" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G63" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="20" t="inlineStr">
-        <is>
-          <t>Jun 29, 2026</t>
-        </is>
-      </c>
-      <c r="I63" s="20" t="inlineStr">
-        <is>
-          <t>18d</t>
-        </is>
-      </c>
-      <c r="J63" s="20" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K63" s="40" t="inlineStr">
+      <c r="K63" s="37" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -12883,22 +13207,22 @@
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>140P6026B0005</t>
+          <t>89503426BWA000067</t>
         </is>
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
+          <t>Denison Substation Stage 10, Iowa</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>Grand Portage, Minnesota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F64" s="17" t="inlineStr">
@@ -12935,22 +13259,22 @@
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>W912PM26BA001</t>
+          <t>140P6026B0005</t>
         </is>
       </c>
       <c r="C65" s="38" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
+          <t>Z--GRPO - Mile Creek Stone Trail Bridge</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Grand Portage, Minnesota</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
@@ -12987,154 +13311,154 @@
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="17" t="inlineStr">
         <is>
+          <t>W912PM26BA001</t>
+        </is>
+      </c>
+      <c r="C66" s="30" t="inlineStr">
+        <is>
+          <t>Atlantic Intracoastal Waterway (AIWW) Snows Cut Shoreline Erosion Bank Stabilization</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>Jun 29, 2026</t>
+        </is>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>18d</t>
+        </is>
+      </c>
+      <c r="J66" s="17" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="B67" s="20" t="inlineStr">
+        <is>
           <t>W9123826RA016</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
+      <c r="C67" s="38" t="inlineStr">
         <is>
           <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D67" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E66" s="17" t="inlineStr">
+      <c r="E67" s="20" t="inlineStr">
         <is>
           <t>237130</t>
         </is>
       </c>
-      <c r="F66" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G66" s="17" t="inlineStr">
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G67" s="20" t="inlineStr">
         <is>
           <t>$23.0M</t>
         </is>
       </c>
-      <c r="H66" s="17" t="inlineStr">
+      <c r="H67" s="20" t="inlineStr">
         <is>
           <t>Jun 29, 2026</t>
         </is>
       </c>
-      <c r="I66" s="17" t="inlineStr">
+      <c r="I67" s="20" t="inlineStr">
         <is>
           <t>18d</t>
         </is>
       </c>
-      <c r="J66" s="17" t="inlineStr">
+      <c r="J67" s="20" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K66" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="B67" s="34" t="inlineStr">
+      <c r="K67" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="B68" s="34" t="inlineStr">
         <is>
           <t>36C10F26B0001</t>
         </is>
       </c>
-      <c r="C67" s="25" t="inlineStr">
+      <c r="C68" s="25" t="inlineStr">
         <is>
           <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
         </is>
       </c>
-      <c r="D67" s="34" t="inlineStr">
+      <c r="D68" s="34" t="inlineStr">
         <is>
           <t>San Antonio, Texas</t>
         </is>
       </c>
-      <c r="E67" s="34" t="inlineStr">
+      <c r="E68" s="34" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F67" s="34" t="inlineStr">
+      <c r="F68" s="34" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G67" s="34" t="inlineStr">
+      <c r="G68" s="34" t="inlineStr">
         <is>
           <t>$1.5M</t>
         </is>
       </c>
-      <c r="H67" s="34" t="inlineStr">
+      <c r="H68" s="34" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="I67" s="34" t="inlineStr">
+      <c r="I68" s="34" t="inlineStr">
         <is>
           <t>19d</t>
         </is>
       </c>
-      <c r="J67" s="34" t="inlineStr">
+      <c r="J68" s="34" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K67" s="37" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>W911WN26BA014</t>
-        </is>
-      </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E68" s="17" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F68" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>$45.0M</t>
-        </is>
-      </c>
-      <c r="H68" s="17" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="I68" s="17" t="inlineStr">
-        <is>
-          <t>19d</t>
-        </is>
-      </c>
-      <c r="J68" s="17" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
+      <c r="K68" s="37" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13143,22 +13467,22 @@
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>12FPC326B0006</t>
+          <t>W911WN26BA014</t>
         </is>
       </c>
       <c r="C69" s="38" t="inlineStr">
         <is>
-          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>Madison, Ohio</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
@@ -13168,7 +13492,7 @@
       </c>
       <c r="G69" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H69" s="20" t="inlineStr">
@@ -13195,22 +13519,22 @@
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>FA481426Q0026</t>
+          <t>12FPC326B0006</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Madison, Ohio</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
@@ -13247,22 +13571,22 @@
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>140P6026B0004</t>
+          <t>140FC226R0002</t>
         </is>
       </c>
       <c r="C71" s="38" t="inlineStr">
         <is>
-          <t>Z--BRVB - Entry Courtyard Improvements</t>
+          <t>MN VLY NWR-HOGBACK LEVEE-FLOOD REPAIR</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>Topeka, Kansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
@@ -13277,12 +13601,12 @@
       </c>
       <c r="H71" s="20" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
@@ -13299,22 +13623,22 @@
     <row r="72" ht="28" customHeight="1">
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0042</t>
+          <t>FA481426Q0026</t>
         </is>
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
@@ -13324,17 +13648,17 @@
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="J72" s="17" t="inlineStr">
@@ -13351,22 +13675,22 @@
     <row r="73" ht="28" customHeight="1">
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>89503326BWA000019</t>
+          <t>140P6026B0004</t>
         </is>
       </c>
       <c r="C73" s="38" t="inlineStr">
         <is>
-          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
+          <t>Z--BRVB - Entry Courtyard Improvements</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Topeka, Kansas</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
@@ -13381,12 +13705,12 @@
       </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="J73" s="20" t="inlineStr">
@@ -13403,22 +13727,22 @@
     <row r="74" ht="28" customHeight="1">
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>191BWC26B0001</t>
+          <t>140P8326Q0042</t>
         </is>
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>Tainter Gates Sandblasting</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>Del Rio, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
@@ -13428,17 +13752,17 @@
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="J74" s="17" t="inlineStr">
@@ -13455,12 +13779,12 @@
     <row r="75" ht="28" customHeight="1">
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>140FGA26R0021</t>
+          <t>140FC226Q0036</t>
         </is>
       </c>
       <c r="C75" s="38" t="inlineStr">
         <is>
-          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
+          <t>VY-MISSISQUOI NWR-PARKING LOT MAINT</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -13470,7 +13794,7 @@
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
@@ -13485,12 +13809,12 @@
       </c>
       <c r="H75" s="20" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 03, 2026</t>
         </is>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="J75" s="20" t="inlineStr">
@@ -13507,12 +13831,12 @@
     <row r="76" ht="28" customHeight="1">
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>W9127N26BA015</t>
+          <t>89503326BWA000019</t>
         </is>
       </c>
       <c r="C76" s="30" t="inlineStr">
         <is>
-          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
+          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
@@ -13522,7 +13846,7 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
@@ -13559,22 +13883,22 @@
     <row r="77" ht="28" customHeight="1">
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>140P8326Q0041</t>
+          <t>191BWC26B0001</t>
         </is>
       </c>
       <c r="C77" s="38" t="inlineStr">
         <is>
-          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
+          <t>Tainter Gates Sandblasting</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Del Rio, Texas</t>
         </is>
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
@@ -13584,7 +13908,7 @@
       </c>
       <c r="G77" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H77" s="20" t="inlineStr">
@@ -13611,17 +13935,17 @@
     <row r="78" ht="28" customHeight="1">
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>W9127826RA046</t>
+          <t>140FGA26R0021</t>
         </is>
       </c>
       <c r="C78" s="30" t="inlineStr">
         <is>
-          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
+          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>Biloxi, Mississippi</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -13641,12 +13965,12 @@
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="I78" s="17" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="J78" s="17" t="inlineStr">
@@ -13663,12 +13987,12 @@
     <row r="79" ht="28" customHeight="1">
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>W912P926BA007</t>
+          <t>W9127N26BA015</t>
         </is>
       </c>
       <c r="C79" s="38" t="inlineStr">
         <is>
-          <t>Crains Island Stage 3</t>
+          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -13693,12 +14017,12 @@
       </c>
       <c r="H79" s="20" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="J79" s="20" t="inlineStr">
@@ -13715,12 +14039,12 @@
     <row r="80" ht="28" customHeight="1">
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>FA282326R0014</t>
+          <t>140P8326Q0041</t>
         </is>
       </c>
       <c r="C80" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
+          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
         </is>
       </c>
       <c r="D80" s="17" t="inlineStr">
@@ -13730,7 +14054,7 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F80" s="17" t="inlineStr">
@@ -13745,12 +14069,12 @@
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="I80" s="17" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="J80" s="17" t="inlineStr">
@@ -13767,22 +14091,22 @@
     <row r="81" ht="28" customHeight="1">
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>140P5326R0006</t>
+          <t>W9127826RA046</t>
         </is>
       </c>
       <c r="C81" s="38" t="inlineStr">
         <is>
-          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
+          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Biloxi, Mississippi</t>
         </is>
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
@@ -13797,12 +14121,12 @@
       </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
-          <t>Jul 08, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="J81" s="20" t="inlineStr">
@@ -13819,12 +14143,12 @@
     <row r="82" ht="28" customHeight="1">
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>140P6426B0008</t>
+          <t>W912P926BA007</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
+          <t>Crains Island Stage 3</t>
         </is>
       </c>
       <c r="D82" s="17" t="inlineStr">
@@ -13849,12 +14173,12 @@
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>Jul 08, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="J82" s="17" t="inlineStr">
@@ -13871,12 +14195,12 @@
     <row r="83" ht="28" customHeight="1">
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>N6247326R9953</t>
+          <t>FA282326R0014</t>
         </is>
       </c>
       <c r="C83" s="38" t="inlineStr">
         <is>
-          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
+          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -13896,17 +14220,17 @@
       </c>
       <c r="G83" s="20" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
@@ -13923,12 +14247,12 @@
     <row r="84" ht="28" customHeight="1">
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>140R4026R0010</t>
+          <t>140P5326R0006</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
+          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
         </is>
       </c>
       <c r="D84" s="17" t="inlineStr">
@@ -13938,7 +14262,7 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
@@ -13953,12 +14277,12 @@
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 08, 2026</t>
         </is>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J84" s="17" t="inlineStr">
@@ -13975,12 +14299,12 @@
     <row r="85" ht="28" customHeight="1">
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>N6247326R0053</t>
+          <t>140P6426B0008</t>
         </is>
       </c>
       <c r="C85" s="38" t="inlineStr">
         <is>
-          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
+          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -13990,7 +14314,7 @@
       </c>
       <c r="E85" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
@@ -14005,12 +14329,12 @@
       </c>
       <c r="H85" s="20" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 08, 2026</t>
         </is>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
@@ -14027,12 +14351,12 @@
     <row r="86" ht="28" customHeight="1">
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>W9128F26RA056</t>
+          <t>N6247326R9953</t>
         </is>
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>Solicitation for Grand Forks Fueling System Repairs</t>
+          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
         </is>
       </c>
       <c r="D86" s="17" t="inlineStr">
@@ -14042,7 +14366,7 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>237120</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
@@ -14079,12 +14403,12 @@
     <row r="87" ht="28" customHeight="1">
       <c r="B87" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>140R4026R0010</t>
         </is>
       </c>
       <c r="C87" s="38" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -14094,7 +14418,7 @@
       </c>
       <c r="E87" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
@@ -14109,12 +14433,12 @@
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>34d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
@@ -14129,52 +14453,52 @@
       </c>
     </row>
     <row r="88" ht="28" customHeight="1">
-      <c r="B88" s="34" t="inlineStr">
-        <is>
-          <t>36C25626R0015</t>
-        </is>
-      </c>
-      <c r="C88" s="25" t="inlineStr">
-        <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
-        </is>
-      </c>
-      <c r="D88" s="34" t="inlineStr">
-        <is>
-          <t>Fayetteville, Arkansas</t>
-        </is>
-      </c>
-      <c r="E88" s="34" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F88" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G88" s="34" t="inlineStr">
-        <is>
-          <t>$15.0M</t>
-        </is>
-      </c>
-      <c r="H88" s="34" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="I88" s="34" t="inlineStr">
-        <is>
-          <t>42d</t>
-        </is>
-      </c>
-      <c r="J88" s="34" t="inlineStr">
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>N6247326R0053</t>
+        </is>
+      </c>
+      <c r="C88" s="30" t="inlineStr">
+        <is>
+          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>Jul 10, 2026</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>29d</t>
+        </is>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K88" s="37" t="inlineStr">
+      <c r="K88" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14183,22 +14507,22 @@
     <row r="89" ht="28" customHeight="1">
       <c r="B89" s="20" t="inlineStr">
         <is>
-          <t>N6247324R0036</t>
+          <t>W9128F26RA056</t>
         </is>
       </c>
       <c r="C89" s="38" t="inlineStr">
         <is>
-          <t>Marine Corps Base Camp Pendleton (MCBCP) Base Operations Support Contract (BOSC)</t>
+          <t>Solicitation for Grand Forks Fueling System Repairs</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
         <is>
-          <t>Oceanside, California</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E89" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237120</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
@@ -14208,17 +14532,17 @@
       </c>
       <c r="G89" s="20" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H89" s="20" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J89" s="20" t="inlineStr">
@@ -14235,22 +14559,22 @@
     <row r="90" ht="28" customHeight="1">
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>140FC226Q0032</t>
+          <t>12445526Q0044</t>
         </is>
       </c>
       <c r="C90" s="30" t="inlineStr">
         <is>
-          <t>VA-HARRISON LAKE NFH-REPL ELECTRICAL VC</t>
+          <t>GAOA Grand Isle NRA Water System Improvement</t>
         </is>
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Munising, Michigan</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
@@ -14265,12 +14589,12 @@
       </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J90" s="17" t="inlineStr">
@@ -14287,12 +14611,12 @@
     <row r="91" ht="28" customHeight="1">
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>W912DR26QA048</t>
+          <t>140L3626Q0032</t>
         </is>
       </c>
       <c r="C91" s="38" t="inlineStr">
         <is>
-          <t>Gravel Road Maintenance</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
@@ -14302,7 +14626,7 @@
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
@@ -14317,124 +14641,124 @@
       </c>
       <c r="H91" s="20" t="inlineStr">
         <is>
+          <t>Jul 15, 2026</t>
+        </is>
+      </c>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>34d</t>
+        </is>
+      </c>
+      <c r="J91" s="20" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K91" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="28" customHeight="1">
+      <c r="B92" s="34" t="inlineStr">
+        <is>
+          <t>36C25626R0015</t>
+        </is>
+      </c>
+      <c r="C92" s="25" t="inlineStr">
+        <is>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+        </is>
+      </c>
+      <c r="D92" s="34" t="inlineStr">
+        <is>
+          <t>Fayetteville, Arkansas</t>
+        </is>
+      </c>
+      <c r="E92" s="34" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F92" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G92" s="34" t="inlineStr">
+        <is>
+          <t>$15.0M</t>
+        </is>
+      </c>
+      <c r="H92" s="34" t="inlineStr">
+        <is>
+          <t>Jul 23, 2026</t>
+        </is>
+      </c>
+      <c r="I92" s="34" t="inlineStr">
+        <is>
+          <t>42d</t>
+        </is>
+      </c>
+      <c r="J92" s="34" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K92" s="37" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="28" customHeight="1">
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>N6247324R0036</t>
+        </is>
+      </c>
+      <c r="C93" s="38" t="inlineStr">
+        <is>
+          <t>Marine Corps Base Camp Pendleton (MCBCP) Base Operations Support Contract (BOSC)</t>
+        </is>
+      </c>
+      <c r="D93" s="20" t="inlineStr">
+        <is>
+          <t>Oceanside, California</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G93" s="20" t="inlineStr">
+        <is>
+          <t>$47.0M</t>
+        </is>
+      </c>
+      <c r="H93" s="20" t="inlineStr">
+        <is>
           <t>Jun 11, 2026</t>
         </is>
       </c>
-      <c r="I91" s="20" t="inlineStr">
+      <c r="I93" s="20" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="J91" s="20" t="inlineStr">
+      <c r="J93" s="20" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K91" s="40" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="28" customHeight="1">
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>FA446026Q0383</t>
-        </is>
-      </c>
-      <c r="C92" s="30" t="inlineStr">
-        <is>
-          <t>Repair/Replace Traffic Lights</t>
-        </is>
-      </c>
-      <c r="D92" s="17" t="inlineStr">
-        <is>
-          <t>Little Rock Air Force Base, Arkansas</t>
-        </is>
-      </c>
-      <c r="E92" s="17" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F92" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G92" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H92" s="17" t="inlineStr">
-        <is>
-          <t>Jun 11, 2026</t>
-        </is>
-      </c>
-      <c r="I92" s="17" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="J92" s="17" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K92" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="28" customHeight="1">
-      <c r="B93" s="34" t="inlineStr">
-        <is>
-          <t>36C24826R0107</t>
-        </is>
-      </c>
-      <c r="C93" s="25" t="inlineStr">
-        <is>
-          <t>J061--PROJECT 675-25-804, Bid-Build (BB) Install Water Tower  Projector System at Lake Nona</t>
-        </is>
-      </c>
-      <c r="D93" s="34" t="inlineStr">
-        <is>
-          <t>Orlando, Florida</t>
-        </is>
-      </c>
-      <c r="E93" s="34" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F93" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G93" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H93" s="34" t="inlineStr">
-        <is>
-          <t>Jun 15, 2026</t>
-        </is>
-      </c>
-      <c r="I93" s="34" t="inlineStr">
-        <is>
-          <t>4d</t>
-        </is>
-      </c>
-      <c r="J93" s="34" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K93" s="37" t="inlineStr">
+      <c r="K93" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14443,12 +14767,12 @@
     <row r="94" ht="28" customHeight="1">
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>W912HN26BA008</t>
+          <t>140FC226Q0032</t>
         </is>
       </c>
       <c r="C94" s="30" t="inlineStr">
         <is>
-          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
+          <t>VA-HARRISON LAKE NFH-REPL ELECTRICAL VC</t>
         </is>
       </c>
       <c r="D94" s="17" t="inlineStr">
@@ -14458,7 +14782,7 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F94" s="17" t="inlineStr">
@@ -14473,17 +14797,17 @@
       </c>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>Jun 15, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J94" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K94" s="32" t="inlineStr">
@@ -14495,12 +14819,12 @@
     <row r="95" ht="28" customHeight="1">
       <c r="B95" s="20" t="inlineStr">
         <is>
-          <t>W912BU26BA026</t>
+          <t>W912DR26QA048</t>
         </is>
       </c>
       <c r="C95" s="38" t="inlineStr">
         <is>
-          <t>Absecon Island Outfalls Repair</t>
+          <t>Gravel Road Maintenance</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -14510,7 +14834,7 @@
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
@@ -14525,17 +14849,17 @@
       </c>
       <c r="H95" s="20" t="inlineStr">
         <is>
-          <t>Jun 16, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="I95" s="20" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J95" s="20" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K95" s="40" t="inlineStr">
@@ -14547,22 +14871,22 @@
     <row r="96" ht="28" customHeight="1">
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>FA301626FB0001</t>
+          <t>FA446026Q0383</t>
         </is>
       </c>
       <c r="C96" s="30" t="inlineStr">
         <is>
-          <t>Repair Carswell Ave.</t>
+          <t>Repair/Replace Traffic Lights</t>
         </is>
       </c>
       <c r="D96" s="17" t="inlineStr">
         <is>
-          <t>DWG, Texas</t>
+          <t>Little Rock Air Force Base, Arkansas</t>
         </is>
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F96" s="17" t="inlineStr">
@@ -14577,17 +14901,17 @@
       </c>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>Jun 17, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J96" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K96" s="32" t="inlineStr">
@@ -14599,102 +14923,102 @@
     <row r="97" ht="28" customHeight="1">
       <c r="B97" s="34" t="inlineStr">
         <is>
-          <t>36C25026B0050</t>
+          <t>36C24826R0107</t>
         </is>
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>Z1DA--Project No. 552-26-202 - Replace Overhead Paging System</t>
+          <t>J061--PROJECT 675-25-804, Bid-Build (BB) Install Water Tower  Projector System at Lake Nona</t>
         </is>
       </c>
       <c r="D97" s="34" t="inlineStr">
         <is>
+          <t>Orlando, Florida</t>
+        </is>
+      </c>
+      <c r="E97" s="34" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F97" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G97" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" s="34" t="inlineStr">
+        <is>
+          <t>Jun 15, 2026</t>
+        </is>
+      </c>
+      <c r="I97" s="34" t="inlineStr">
+        <is>
+          <t>4d</t>
+        </is>
+      </c>
+      <c r="J97" s="34" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K97" s="37" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="28" customHeight="1">
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>W912HN26BA008</t>
+        </is>
+      </c>
+      <c r="C98" s="30" t="inlineStr">
+        <is>
+          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E97" s="34" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F97" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G97" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H97" s="34" t="inlineStr">
-        <is>
-          <t>Jun 17, 2026</t>
-        </is>
-      </c>
-      <c r="I97" s="34" t="inlineStr">
-        <is>
-          <t>6d</t>
-        </is>
-      </c>
-      <c r="J97" s="34" t="inlineStr">
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H98" s="17" t="inlineStr">
+        <is>
+          <t>Jun 15, 2026</t>
+        </is>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>4d</t>
+        </is>
+      </c>
+      <c r="J98" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K97" s="37" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="28" customHeight="1">
-      <c r="B98" s="34" t="inlineStr">
-        <is>
-          <t>36C25026B0045</t>
-        </is>
-      </c>
-      <c r="C98" s="25" t="inlineStr">
-        <is>
-          <t>Z2LC--Campus Sinkhole Repair  552-26-506</t>
-        </is>
-      </c>
-      <c r="D98" s="34" t="inlineStr">
-        <is>
-          <t>Dayton, Ohio</t>
-        </is>
-      </c>
-      <c r="E98" s="34" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F98" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G98" s="34" t="inlineStr">
-        <is>
-          <t>$750K</t>
-        </is>
-      </c>
-      <c r="H98" s="34" t="inlineStr">
-        <is>
-          <t>Jun 18, 2026</t>
-        </is>
-      </c>
-      <c r="I98" s="34" t="inlineStr">
-        <is>
-          <t>7d</t>
-        </is>
-      </c>
-      <c r="J98" s="34" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K98" s="37" t="inlineStr">
+      <c r="K98" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14703,12 +15027,12 @@
     <row r="99" ht="28" customHeight="1">
       <c r="B99" s="20" t="inlineStr">
         <is>
-          <t>W911WN26RA011</t>
+          <t>W912BU26BA026</t>
         </is>
       </c>
       <c r="C99" s="38" t="inlineStr">
         <is>
-          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
+          <t>Absecon Island Outfalls Repair</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -14733,12 +15057,12 @@
       </c>
       <c r="H99" s="20" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jun 16, 2026</t>
         </is>
       </c>
       <c r="I99" s="20" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J99" s="20" t="inlineStr">
@@ -14755,154 +15079,154 @@
     <row r="100" ht="28" customHeight="1">
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>140P6026Q0052</t>
+          <t>FA301626FB0001</t>
         </is>
       </c>
       <c r="C100" s="30" t="inlineStr">
         <is>
-          <t>Z--WACO Emergency Generator</t>
+          <t>Repair Carswell Ave.</t>
         </is>
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t>Waco, Texas</t>
+          <t>DWG, Texas</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H100" s="17" t="inlineStr">
+        <is>
+          <t>Jun 17, 2026</t>
+        </is>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="J100" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K100" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="B101" s="34" t="inlineStr">
+        <is>
+          <t>36C25026B0050</t>
+        </is>
+      </c>
+      <c r="C101" s="25" t="inlineStr">
+        <is>
+          <t>Z1DA--Project No. 552-26-202 - Replace Overhead Paging System</t>
+        </is>
+      </c>
+      <c r="D101" s="34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E101" s="34" t="inlineStr">
+        <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F100" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G100" s="17" t="inlineStr">
-        <is>
-          <t>$62K</t>
-        </is>
-      </c>
-      <c r="H100" s="17" t="inlineStr">
+      <c r="F101" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G101" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H101" s="34" t="inlineStr">
+        <is>
+          <t>Jun 17, 2026</t>
+        </is>
+      </c>
+      <c r="I101" s="34" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="J101" s="34" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K101" s="37" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="B102" s="34" t="inlineStr">
+        <is>
+          <t>36C25026B0045</t>
+        </is>
+      </c>
+      <c r="C102" s="25" t="inlineStr">
+        <is>
+          <t>Z2LC--Campus Sinkhole Repair  552-26-506</t>
+        </is>
+      </c>
+      <c r="D102" s="34" t="inlineStr">
+        <is>
+          <t>Dayton, Ohio</t>
+        </is>
+      </c>
+      <c r="E102" s="34" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F102" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G102" s="34" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+      <c r="H102" s="34" t="inlineStr">
         <is>
           <t>Jun 18, 2026</t>
         </is>
       </c>
-      <c r="I100" s="17" t="inlineStr">
+      <c r="I102" s="34" t="inlineStr">
         <is>
           <t>7d</t>
         </is>
       </c>
-      <c r="J100" s="17" t="inlineStr">
+      <c r="J102" s="34" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K100" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="28" customHeight="1">
-      <c r="B101" s="20" t="inlineStr">
-        <is>
-          <t>36C25226Q0426</t>
-        </is>
-      </c>
-      <c r="C101" s="38" t="inlineStr">
-        <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
-        </is>
-      </c>
-      <c r="D101" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E101" s="20" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F101" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G101" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H101" s="20" t="inlineStr">
-        <is>
-          <t>Jun 22, 2026</t>
-        </is>
-      </c>
-      <c r="I101" s="20" t="inlineStr">
-        <is>
-          <t>11d</t>
-        </is>
-      </c>
-      <c r="J101" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K101" s="40" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="28" customHeight="1">
-      <c r="B102" s="17" t="inlineStr">
-        <is>
-          <t>36C24526Q0576</t>
-        </is>
-      </c>
-      <c r="C102" s="30" t="inlineStr">
-        <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
-        </is>
-      </c>
-      <c r="D102" s="17" t="inlineStr">
-        <is>
-          <t>Baltimore, MD</t>
-        </is>
-      </c>
-      <c r="E102" s="17" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F102" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G102" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H102" s="17" t="inlineStr">
-        <is>
-          <t>Jun 22, 2026</t>
-        </is>
-      </c>
-      <c r="I102" s="17" t="inlineStr">
-        <is>
-          <t>11d</t>
-        </is>
-      </c>
-      <c r="J102" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K102" s="32" t="inlineStr">
+      <c r="K102" s="37" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14911,22 +15235,22 @@
     <row r="103" ht="28" customHeight="1">
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>FDA-PRESOL-132892</t>
+          <t>W911WN26RA011</t>
         </is>
       </c>
       <c r="C103" s="38" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -14936,17 +15260,17 @@
       </c>
       <c r="G103" s="20" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H103" s="20" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I103" s="20" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J103" s="20" t="inlineStr">
@@ -14963,22 +15287,22 @@
     <row r="104" ht="28" customHeight="1">
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>W912PM26RA0003</t>
+          <t>140P6026Q0052</t>
         </is>
       </c>
       <c r="C104" s="30" t="inlineStr">
         <is>
-          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
+          <t>Z--WACO Emergency Generator</t>
         </is>
       </c>
       <c r="D104" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Waco, Texas</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F104" s="17" t="inlineStr">
@@ -14988,17 +15312,17 @@
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="H104" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J104" s="17" t="inlineStr">
@@ -15015,12 +15339,12 @@
     <row r="105" ht="28" customHeight="1">
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>W50S7X-26-B-A003</t>
+          <t>36C25226Q0426</t>
         </is>
       </c>
       <c r="C105" s="38" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -15040,17 +15364,17 @@
       </c>
       <c r="G105" s="20" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H105" s="20" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I105" s="20" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>11d</t>
         </is>
       </c>
       <c r="J105" s="20" t="inlineStr">
@@ -15067,22 +15391,22 @@
     <row r="106" ht="28" customHeight="1">
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>GROUP1-24-R-W001</t>
+          <t>36C24526Q0576</t>
         </is>
       </c>
       <c r="C106" s="30" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D106" s="17" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F106" s="17" t="inlineStr">
@@ -15092,17 +15416,17 @@
       </c>
       <c r="G106" s="17" t="inlineStr">
         <is>
-          <t>$17.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>11d</t>
         </is>
       </c>
       <c r="J106" s="17" t="inlineStr">
@@ -15117,52 +15441,52 @@
       </c>
     </row>
     <row r="107" ht="28" customHeight="1">
-      <c r="B107" s="34" t="inlineStr">
-        <is>
-          <t>36C26126R0050</t>
-        </is>
-      </c>
-      <c r="C107" s="25" t="inlineStr">
-        <is>
-          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
-        </is>
-      </c>
-      <c r="D107" s="34" t="inlineStr">
-        <is>
-          <t>Reno, NV</t>
-        </is>
-      </c>
-      <c r="E107" s="34" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F107" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G107" s="34" t="inlineStr">
-        <is>
-          <t>$5.0M</t>
-        </is>
-      </c>
-      <c r="H107" s="34" t="inlineStr">
-        <is>
-          <t>Jun 24, 2026</t>
-        </is>
-      </c>
-      <c r="I107" s="34" t="inlineStr">
-        <is>
-          <t>13d</t>
-        </is>
-      </c>
-      <c r="J107" s="34" t="inlineStr">
+      <c r="B107" s="20" t="inlineStr">
+        <is>
+          <t>FDA-PRESOL-132892</t>
+        </is>
+      </c>
+      <c r="C107" s="38" t="inlineStr">
+        <is>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+        </is>
+      </c>
+      <c r="D107" s="20" t="inlineStr">
+        <is>
+          <t>Jefferson, Arkansas</t>
+        </is>
+      </c>
+      <c r="E107" s="20" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F107" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G107" s="20" t="inlineStr">
+        <is>
+          <t>$47.0M</t>
+        </is>
+      </c>
+      <c r="H107" s="20" t="inlineStr">
+        <is>
+          <t>Jun 22, 2026</t>
+        </is>
+      </c>
+      <c r="I107" s="20" t="inlineStr">
+        <is>
+          <t>11d</t>
+        </is>
+      </c>
+      <c r="J107" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K107" s="37" t="inlineStr">
+      <c r="K107" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15171,12 +15495,12 @@
     <row r="108" ht="28" customHeight="1">
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>693C73-26-R-000047</t>
+          <t>W912PM26RA0003</t>
         </is>
       </c>
       <c r="C108" s="30" t="inlineStr">
         <is>
-          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
+          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
         </is>
       </c>
       <c r="D108" s="17" t="inlineStr">
@@ -15186,7 +15510,7 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F108" s="17" t="inlineStr">
@@ -15196,17 +15520,17 @@
       </c>
       <c r="G108" s="17" t="inlineStr">
         <is>
-          <t>$12.9M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I108" s="17" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="J108" s="17" t="inlineStr">
@@ -15223,22 +15547,22 @@
     <row r="109" ht="28" customHeight="1">
       <c r="B109" s="20" t="inlineStr">
         <is>
-          <t>W9128F26BA019</t>
+          <t>W50S7X-26-B-A003</t>
         </is>
       </c>
       <c r="C109" s="38" t="inlineStr">
         <is>
-          <t>Oahe IDCC Road Maintenance 2026</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
         <is>
-          <t>Fort Pierre, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -15248,17 +15572,17 @@
       </c>
       <c r="G109" s="20" t="inlineStr">
         <is>
-          <t>$21.5M</t>
+          <t>$5.1M</t>
         </is>
       </c>
       <c r="H109" s="20" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I109" s="20" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="J109" s="20" t="inlineStr">
@@ -15273,104 +15597,104 @@
       </c>
     </row>
     <row r="110" ht="28" customHeight="1">
-      <c r="B110" s="34" t="inlineStr">
-        <is>
-          <t>36C24626R0067</t>
-        </is>
-      </c>
-      <c r="C110" s="25" t="inlineStr">
-        <is>
-          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
-        </is>
-      </c>
-      <c r="D110" s="34" t="inlineStr">
-        <is>
-          <t>Hampton, Virginia</t>
-        </is>
-      </c>
-      <c r="E110" s="34" t="inlineStr">
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>GROUP1-24-R-W001</t>
+        </is>
+      </c>
+      <c r="C110" s="30" t="inlineStr">
+        <is>
+          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F110" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="inlineStr">
+        <is>
+          <t>$17.5M</t>
+        </is>
+      </c>
+      <c r="H110" s="17" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>13d</t>
+        </is>
+      </c>
+      <c r="J110" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K110" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="B111" s="34" t="inlineStr">
+        <is>
+          <t>36C26126R0050</t>
+        </is>
+      </c>
+      <c r="C111" s="25" t="inlineStr">
+        <is>
+          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
+        </is>
+      </c>
+      <c r="D111" s="34" t="inlineStr">
+        <is>
+          <t>Reno, NV</t>
+        </is>
+      </c>
+      <c r="E111" s="34" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F110" s="34" t="inlineStr">
+      <c r="F111" s="34" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G110" s="34" t="inlineStr">
-        <is>
-          <t>$7.0M</t>
-        </is>
-      </c>
-      <c r="H110" s="34" t="inlineStr">
-        <is>
-          <t>Jul 13, 2026</t>
-        </is>
-      </c>
-      <c r="I110" s="34" t="inlineStr">
-        <is>
-          <t>32d</t>
-        </is>
-      </c>
-      <c r="J110" s="34" t="inlineStr">
+      <c r="G111" s="34" t="inlineStr">
+        <is>
+          <t>$5.0M</t>
+        </is>
+      </c>
+      <c r="H111" s="34" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I111" s="34" t="inlineStr">
+        <is>
+          <t>13d</t>
+        </is>
+      </c>
+      <c r="J111" s="34" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K110" s="37" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="B111" s="20" t="inlineStr">
-        <is>
-          <t>140L2626R0004</t>
-        </is>
-      </c>
-      <c r="C111" s="38" t="inlineStr">
-        <is>
-          <t>Y--Cauldron Linn Recreation Site Improvements</t>
-        </is>
-      </c>
-      <c r="D111" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E111" s="20" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F111" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G111" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H111" s="20" t="inlineStr">
-        <is>
-          <t>Jul 13, 2026</t>
-        </is>
-      </c>
-      <c r="I111" s="20" t="inlineStr">
-        <is>
-          <t>32d</t>
-        </is>
-      </c>
-      <c r="J111" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K111" s="40" t="inlineStr">
+      <c r="K111" s="37" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15379,12 +15703,12 @@
     <row r="112" ht="28" customHeight="1">
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0032</t>
+          <t>693C73-26-R-000047</t>
         </is>
       </c>
       <c r="C112" s="30" t="inlineStr">
         <is>
-          <t>Y--Indian Springs Vault Toilet</t>
+          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
         </is>
       </c>
       <c r="D112" s="17" t="inlineStr">
@@ -15394,7 +15718,7 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F112" s="17" t="inlineStr">
@@ -15404,17 +15728,17 @@
       </c>
       <c r="G112" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$12.9M</t>
         </is>
       </c>
       <c r="H112" s="17" t="inlineStr">
         <is>
-          <t>Jul 13, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I112" s="17" t="inlineStr">
         <is>
-          <t>32d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="J112" s="17" t="inlineStr">
@@ -15431,22 +15755,22 @@
     <row r="113" ht="28" customHeight="1">
       <c r="B113" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000068</t>
+          <t>W9128F26BA019</t>
         </is>
       </c>
       <c r="C113" s="38" t="inlineStr">
         <is>
-          <t>Y--Beresford Substation Stage 11, South Dakota</t>
+          <t>Oahe IDCC Road Maintenance 2026</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Fort Pierre, South Dakota</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -15456,17 +15780,17 @@
       </c>
       <c r="G113" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$21.5M</t>
         </is>
       </c>
       <c r="H113" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I113" s="20" t="inlineStr">
         <is>
-          <t>34d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="J113" s="20" t="inlineStr">
@@ -15481,52 +15805,52 @@
       </c>
     </row>
     <row r="114" ht="28" customHeight="1">
-      <c r="B114" s="17" t="inlineStr">
-        <is>
-          <t>W912EE26RA015</t>
-        </is>
-      </c>
-      <c r="C114" s="30" t="inlineStr">
-        <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
-        </is>
-      </c>
-      <c r="D114" s="17" t="inlineStr">
-        <is>
-          <t>Royal, Arkansas</t>
-        </is>
-      </c>
-      <c r="E114" s="17" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F114" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G114" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H114" s="17" t="inlineStr">
-        <is>
-          <t>Jul 15, 2026</t>
-        </is>
-      </c>
-      <c r="I114" s="17" t="inlineStr">
-        <is>
-          <t>34d</t>
-        </is>
-      </c>
-      <c r="J114" s="17" t="inlineStr">
+      <c r="B114" s="34" t="inlineStr">
+        <is>
+          <t>36C24626R0067</t>
+        </is>
+      </c>
+      <c r="C114" s="25" t="inlineStr">
+        <is>
+          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
+        </is>
+      </c>
+      <c r="D114" s="34" t="inlineStr">
+        <is>
+          <t>Hampton, Virginia</t>
+        </is>
+      </c>
+      <c r="E114" s="34" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F114" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G114" s="34" t="inlineStr">
+        <is>
+          <t>$7.0M</t>
+        </is>
+      </c>
+      <c r="H114" s="34" t="inlineStr">
+        <is>
+          <t>Jul 13, 2026</t>
+        </is>
+      </c>
+      <c r="I114" s="34" t="inlineStr">
+        <is>
+          <t>32d</t>
+        </is>
+      </c>
+      <c r="J114" s="34" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K114" s="32" t="inlineStr">
+      <c r="K114" s="37" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15535,12 +15859,12 @@
     <row r="115" ht="28" customHeight="1">
       <c r="B115" s="20" t="inlineStr">
         <is>
-          <t>140L2626R0003</t>
+          <t>140L2626R0004</t>
         </is>
       </c>
       <c r="C115" s="38" t="inlineStr">
         <is>
-          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
+          <t>Y--Cauldron Linn Recreation Site Improvements</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
@@ -15550,7 +15874,7 @@
       </c>
       <c r="E115" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -15565,12 +15889,12 @@
       </c>
       <c r="H115" s="20" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I115" s="20" t="inlineStr">
         <is>
-          <t>41d</t>
+          <t>32d</t>
         </is>
       </c>
       <c r="J115" s="20" t="inlineStr">
@@ -15587,12 +15911,12 @@
     <row r="116" ht="28" customHeight="1">
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0033</t>
+          <t>140L2626Q0032</t>
         </is>
       </c>
       <c r="C116" s="30" t="inlineStr">
         <is>
-          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
+          <t>Y--Indian Springs Vault Toilet</t>
         </is>
       </c>
       <c r="D116" s="17" t="inlineStr">
@@ -15617,12 +15941,12 @@
       </c>
       <c r="H116" s="17" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I116" s="17" t="inlineStr">
         <is>
-          <t>41d</t>
+          <t>32d</t>
         </is>
       </c>
       <c r="J116" s="17" t="inlineStr">
@@ -15639,12 +15963,12 @@
     <row r="117" ht="28" customHeight="1">
       <c r="B117" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0016</t>
+          <t>89503426BWA000068</t>
         </is>
       </c>
       <c r="C117" s="38" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Y--Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
@@ -15654,7 +15978,7 @@
       </c>
       <c r="E117" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -15669,12 +15993,12 @@
       </c>
       <c r="H117" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I117" s="20" t="inlineStr">
         <is>
-          <t>43d</t>
+          <t>34d</t>
         </is>
       </c>
       <c r="J117" s="20" t="inlineStr">
@@ -15691,22 +16015,22 @@
     <row r="118" ht="28" customHeight="1">
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0015</t>
+          <t>W912EE26RA015</t>
         </is>
       </c>
       <c r="C118" s="30" t="inlineStr">
         <is>
-          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D118" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F118" s="17" t="inlineStr">
@@ -15721,12 +16045,12 @@
       </c>
       <c r="H118" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
-          <t>43d</t>
+          <t>34d</t>
         </is>
       </c>
       <c r="J118" s="17" t="inlineStr">
@@ -15743,12 +16067,12 @@
     <row r="119" ht="28" customHeight="1">
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0017</t>
+          <t>140L2626R0003</t>
         </is>
       </c>
       <c r="C119" s="38" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
@@ -15758,7 +16082,7 @@
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
@@ -15773,12 +16097,12 @@
       </c>
       <c r="H119" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I119" s="20" t="inlineStr">
         <is>
-          <t>43d</t>
+          <t>41d</t>
         </is>
       </c>
       <c r="J119" s="20" t="inlineStr">
@@ -15795,12 +16119,12 @@
     <row r="120" ht="28" customHeight="1">
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0024</t>
+          <t>140L2626Q0033</t>
         </is>
       </c>
       <c r="C120" s="30" t="inlineStr">
         <is>
-          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
+          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
         </is>
       </c>
       <c r="D120" s="17" t="inlineStr">
@@ -15810,7 +16134,7 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F120" s="17" t="inlineStr">
@@ -15820,17 +16144,17 @@
       </c>
       <c r="G120" s="17" t="inlineStr">
         <is>
-          <t>$11.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H120" s="17" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
-          <t>46d</t>
+          <t>41d</t>
         </is>
       </c>
       <c r="J120" s="17" t="inlineStr">
@@ -15847,12 +16171,12 @@
     <row r="121" ht="28" customHeight="1">
       <c r="B121" s="20" t="inlineStr">
         <is>
-          <t>140L3726R0006</t>
+          <t>140P5426R0016</t>
         </is>
       </c>
       <c r="C121" s="38" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
@@ -15862,7 +16186,7 @@
       </c>
       <c r="E121" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
@@ -15872,17 +16196,17 @@
       </c>
       <c r="G121" s="20" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H121" s="20" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I121" s="20" t="inlineStr">
         <is>
-          <t>78d</t>
+          <t>43d</t>
         </is>
       </c>
       <c r="J121" s="20" t="inlineStr">
@@ -15899,17 +16223,17 @@
     <row r="122" ht="28" customHeight="1">
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>W9123826BA011</t>
+          <t>140P5426R0015</t>
         </is>
       </c>
       <c r="C122" s="30" t="inlineStr">
         <is>
-          <t>Rail Curves Package 3 for MOTCO, CA</t>
+          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
         </is>
       </c>
       <c r="D122" s="17" t="inlineStr">
         <is>
-          <t>Concord, California</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E122" s="17" t="inlineStr">
@@ -15924,17 +16248,17 @@
       </c>
       <c r="G122" s="17" t="inlineStr">
         <is>
-          <t>$7.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H122" s="17" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>43d</t>
         </is>
       </c>
       <c r="J122" s="17" t="inlineStr">
@@ -15951,22 +16275,22 @@
     <row r="123" ht="28" customHeight="1">
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>EQPMBE-26-0203</t>
+          <t>140P5426R0017</t>
         </is>
       </c>
       <c r="C123" s="38" t="inlineStr">
         <is>
-          <t>USAO Schwartz Conference Room Display Upgrade</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
@@ -15981,12 +16305,12 @@
       </c>
       <c r="H123" s="20" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I123" s="20" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>43d</t>
         </is>
       </c>
       <c r="J123" s="20" t="inlineStr">
@@ -16003,12 +16327,12 @@
     <row r="124" ht="28" customHeight="1">
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>140P5326R0019</t>
+          <t>140FGA26R0024</t>
         </is>
       </c>
       <c r="C124" s="30" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
         </is>
       </c>
       <c r="D124" s="17" t="inlineStr">
@@ -16018,7 +16342,7 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
@@ -16028,17 +16352,17 @@
       </c>
       <c r="G124" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.5M</t>
         </is>
       </c>
       <c r="H124" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jul 27, 2026</t>
         </is>
       </c>
       <c r="I124" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46d</t>
         </is>
       </c>
       <c r="J124" s="17" t="inlineStr">
@@ -16053,52 +16377,52 @@
       </c>
     </row>
     <row r="125" ht="28" customHeight="1">
-      <c r="B125" s="34" t="inlineStr">
-        <is>
-          <t>36C25726B0007</t>
-        </is>
-      </c>
-      <c r="C125" s="25" t="inlineStr">
-        <is>
-          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
-        </is>
-      </c>
-      <c r="D125" s="34" t="inlineStr">
-        <is>
-          <t>Waco, Texas</t>
-        </is>
-      </c>
-      <c r="E125" s="34" t="inlineStr">
+      <c r="B125" s="20" t="inlineStr">
+        <is>
+          <t>140L3726R0006</t>
+        </is>
+      </c>
+      <c r="C125" s="38" t="inlineStr">
+        <is>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+        </is>
+      </c>
+      <c r="D125" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E125" s="20" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F125" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G125" s="34" t="inlineStr">
-        <is>
-          <t>$2.5B</t>
-        </is>
-      </c>
-      <c r="H125" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I125" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J125" s="34" t="inlineStr">
+      <c r="F125" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G125" s="20" t="inlineStr">
+        <is>
+          <t>$19.0M</t>
+        </is>
+      </c>
+      <c r="H125" s="20" t="inlineStr">
+        <is>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="I125" s="20" t="inlineStr">
+        <is>
+          <t>78d</t>
+        </is>
+      </c>
+      <c r="J125" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K125" s="37" t="inlineStr">
+      <c r="K125" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16107,17 +16431,17 @@
     <row r="126" ht="28" customHeight="1">
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>W912HY26BA030</t>
+          <t>W9123826BA011</t>
         </is>
       </c>
       <c r="C126" s="30" t="inlineStr">
         <is>
-          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
+          <t>Rail Curves Package 3 for MOTCO, CA</t>
         </is>
       </c>
       <c r="D126" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concord, California</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr">
@@ -16132,17 +16456,17 @@
       </c>
       <c r="G126" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$7.5M</t>
         </is>
       </c>
       <c r="H126" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="I126" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J126" s="17" t="inlineStr">
@@ -16159,22 +16483,22 @@
     <row r="127" ht="28" customHeight="1">
       <c r="B127" s="20" t="inlineStr">
         <is>
-          <t>W912ES26BA013</t>
+          <t>EQPMBE-26-0203</t>
         </is>
       </c>
       <c r="C127" s="38" t="inlineStr">
         <is>
-          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
+          <t>USAO Schwartz Conference Room Display Upgrade</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>California</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -16189,12 +16513,12 @@
       </c>
       <c r="H127" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="I127" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J127" s="20" t="inlineStr">
@@ -16211,12 +16535,12 @@
     <row r="128" ht="28" customHeight="1">
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>W912WJ26QA119</t>
+          <t>140P5326R0019</t>
         </is>
       </c>
       <c r="C128" s="30" t="inlineStr">
         <is>
-          <t>Storage Building Parking Lot Installation and Paving, Buffumville Lake, Charlton, MA</t>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
       <c r="D128" s="17" t="inlineStr">
@@ -16226,7 +16550,7 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F128" s="17" t="inlineStr">
@@ -16236,7 +16560,7 @@
       </c>
       <c r="G128" s="17" t="inlineStr">
         <is>
-          <t>$175K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H128" s="17" t="inlineStr">
@@ -16261,52 +16585,52 @@
       </c>
     </row>
     <row r="129" ht="28" customHeight="1">
-      <c r="B129" s="20" t="inlineStr">
-        <is>
-          <t>W911WN26BA008</t>
-        </is>
-      </c>
-      <c r="C129" s="38" t="inlineStr">
-        <is>
-          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
-        </is>
-      </c>
-      <c r="D129" s="20" t="inlineStr">
-        <is>
-          <t>Saltsburg, Pennsylvania</t>
-        </is>
-      </c>
-      <c r="E129" s="20" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F129" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G129" s="20" t="inlineStr">
-        <is>
-          <t>$45.0M</t>
-        </is>
-      </c>
-      <c r="H129" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I129" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J129" s="20" t="inlineStr">
+      <c r="B129" s="34" t="inlineStr">
+        <is>
+          <t>36C25726B0007</t>
+        </is>
+      </c>
+      <c r="C129" s="25" t="inlineStr">
+        <is>
+          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
+        </is>
+      </c>
+      <c r="D129" s="34" t="inlineStr">
+        <is>
+          <t>Waco, Texas</t>
+        </is>
+      </c>
+      <c r="E129" s="34" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F129" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G129" s="34" t="inlineStr">
+        <is>
+          <t>$2.5B</t>
+        </is>
+      </c>
+      <c r="H129" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I129" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J129" s="34" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K129" s="40" t="inlineStr">
+      <c r="K129" s="37" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16315,12 +16639,12 @@
     <row r="130" ht="28" customHeight="1">
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>PANNWD26P0000028054</t>
+          <t>W912HY26BA030</t>
         </is>
       </c>
       <c r="C130" s="30" t="inlineStr">
         <is>
-          <t>Levee Repair at MRLS L246</t>
+          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
         </is>
       </c>
       <c r="D130" s="17" t="inlineStr">
@@ -16340,7 +16664,7 @@
       </c>
       <c r="G130" s="17" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H130" s="17" t="inlineStr">
@@ -16367,22 +16691,22 @@
     <row r="131" ht="28" customHeight="1">
       <c r="B131" s="20" t="inlineStr">
         <is>
-          <t>75H70126R00030</t>
+          <t>W912ES26BA013</t>
         </is>
       </c>
       <c r="C131" s="38" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
@@ -16392,7 +16716,7 @@
       </c>
       <c r="G131" s="20" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H131" s="20" t="inlineStr">
@@ -16419,12 +16743,12 @@
     <row r="132" ht="28" customHeight="1">
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0028</t>
+          <t>W912WJ26QA119</t>
         </is>
       </c>
       <c r="C132" s="30" t="inlineStr">
         <is>
-          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+          <t>Storage Building Parking Lot Installation and Paving, Buffumville Lake, Charlton, MA</t>
         </is>
       </c>
       <c r="D132" s="17" t="inlineStr">
@@ -16444,7 +16768,7 @@
       </c>
       <c r="G132" s="17" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>$175K</t>
         </is>
       </c>
       <c r="H132" s="17" t="inlineStr">
@@ -16471,102 +16795,102 @@
     <row r="133" ht="28" customHeight="1">
       <c r="B133" s="20" t="inlineStr">
         <is>
-          <t>W9128F26RA107</t>
+          <t>W911WN26BA008</t>
         </is>
       </c>
       <c r="C133" s="38" t="inlineStr">
         <is>
-          <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
+          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
         <is>
+          <t>Saltsburg, Pennsylvania</t>
+        </is>
+      </c>
+      <c r="E133" s="20" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F133" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G133" s="20" t="inlineStr">
+        <is>
+          <t>$45.0M</t>
+        </is>
+      </c>
+      <c r="H133" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I133" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J133" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K133" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="28" customHeight="1">
+      <c r="B134" s="17" t="inlineStr">
+        <is>
+          <t>PANNWD26P0000028054</t>
+        </is>
+      </c>
+      <c r="C134" s="30" t="inlineStr">
+        <is>
+          <t>Levee Repair at MRLS L246</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr">
+        <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E133" s="20" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F133" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G133" s="20" t="inlineStr">
-        <is>
-          <t>$30.0M</t>
-        </is>
-      </c>
-      <c r="H133" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I133" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J133" s="20" t="inlineStr">
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G134" s="17" t="inlineStr">
+        <is>
+          <t>$3.0M</t>
+        </is>
+      </c>
+      <c r="H134" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J134" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K133" s="40" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="28" customHeight="1">
-      <c r="B134" s="34" t="inlineStr">
-        <is>
-          <t>36C24226B0057</t>
-        </is>
-      </c>
-      <c r="C134" s="25" t="inlineStr">
-        <is>
-          <t>N091--PROJECT # 528-18-110  Fuel Oil Tank Replacement  BUFFALO VAMC</t>
-        </is>
-      </c>
-      <c r="D134" s="34" t="inlineStr">
-        <is>
-          <t>Buffalo, New York</t>
-        </is>
-      </c>
-      <c r="E134" s="34" t="inlineStr">
-        <is>
-          <t>237120</t>
-        </is>
-      </c>
-      <c r="F134" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G134" s="34" t="inlineStr">
-        <is>
-          <t>$16.2M</t>
-        </is>
-      </c>
-      <c r="H134" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I134" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J134" s="34" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K134" s="37" t="inlineStr">
+      <c r="K134" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16575,22 +16899,22 @@
     <row r="135" ht="28" customHeight="1">
       <c r="B135" s="20" t="inlineStr">
         <is>
-          <t>12445526Q0069</t>
+          <t>75H70126R00030</t>
         </is>
       </c>
       <c r="C135" s="38" t="inlineStr">
         <is>
-          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+          <t>Rosebud Lift Station Construction</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Rosebud, South Dakota</t>
         </is>
       </c>
       <c r="E135" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
@@ -16600,22 +16924,22 @@
       </c>
       <c r="G135" s="20" t="inlineStr">
         <is>
-          <t>$25K</t>
+          <t>$750K</t>
         </is>
       </c>
       <c r="H135" s="20" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I135" s="20" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J135" s="20" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K135" s="40" t="inlineStr">
@@ -16627,12 +16951,12 @@
     <row r="136" ht="28" customHeight="1">
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>SP470525R002026</t>
+          <t>140FGA26R0028</t>
         </is>
       </c>
       <c r="C136" s="30" t="inlineStr">
         <is>
-          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
         </is>
       </c>
       <c r="D136" s="17" t="inlineStr">
@@ -16642,7 +16966,7 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F136" s="17" t="inlineStr">
@@ -16652,22 +16976,22 @@
       </c>
       <c r="G136" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.8M</t>
         </is>
       </c>
       <c r="H136" s="17" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I136" s="17" t="inlineStr">
         <is>
-          <t>19d</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J136" s="17" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K136" s="32" t="inlineStr">
@@ -16679,57 +17003,317 @@
     <row r="137" ht="28" customHeight="1">
       <c r="B137" s="20" t="inlineStr">
         <is>
+          <t>W9128F26RA107</t>
+        </is>
+      </c>
+      <c r="C137" s="38" t="inlineStr">
+        <is>
+          <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
+        </is>
+      </c>
+      <c r="D137" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E137" s="20" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F137" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G137" s="20" t="inlineStr">
+        <is>
+          <t>$30.0M</t>
+        </is>
+      </c>
+      <c r="H137" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I137" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J137" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K137" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="28" customHeight="1">
+      <c r="B138" s="34" t="inlineStr">
+        <is>
+          <t>36C24226B0057</t>
+        </is>
+      </c>
+      <c r="C138" s="25" t="inlineStr">
+        <is>
+          <t>N091--PROJECT # 528-18-110  Fuel Oil Tank Replacement  BUFFALO VAMC</t>
+        </is>
+      </c>
+      <c r="D138" s="34" t="inlineStr">
+        <is>
+          <t>Buffalo, New York</t>
+        </is>
+      </c>
+      <c r="E138" s="34" t="inlineStr">
+        <is>
+          <t>237120</t>
+        </is>
+      </c>
+      <c r="F138" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G138" s="34" t="inlineStr">
+        <is>
+          <t>$16.2M</t>
+        </is>
+      </c>
+      <c r="H138" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I138" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J138" s="34" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K138" s="37" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="28" customHeight="1">
+      <c r="B139" s="20" t="inlineStr">
+        <is>
+          <t>140P6326B0008</t>
+        </is>
+      </c>
+      <c r="C139" s="38" t="inlineStr">
+        <is>
+          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
+        </is>
+      </c>
+      <c r="D139" s="20" t="inlineStr">
+        <is>
+          <t>Medora, North Dakota</t>
+        </is>
+      </c>
+      <c r="E139" s="20" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F139" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G139" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H139" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I139" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J139" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K139" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="28" customHeight="1">
+      <c r="B140" s="17" t="inlineStr">
+        <is>
+          <t>12445526Q0069</t>
+        </is>
+      </c>
+      <c r="C140" s="30" t="inlineStr">
+        <is>
+          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E140" s="17" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G140" s="17" t="inlineStr">
+        <is>
+          <t>$25K</t>
+        </is>
+      </c>
+      <c r="H140" s="17" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>13d</t>
+        </is>
+      </c>
+      <c r="J140" s="17" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K140" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="B141" s="20" t="inlineStr">
+        <is>
+          <t>SP470525R002026</t>
+        </is>
+      </c>
+      <c r="C141" s="38" t="inlineStr">
+        <is>
+          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+        </is>
+      </c>
+      <c r="D141" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E141" s="20" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F141" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G141" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H141" s="20" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="I141" s="20" t="inlineStr">
+        <is>
+          <t>19d</t>
+        </is>
+      </c>
+      <c r="J141" s="20" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K141" s="40" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="28" customHeight="1">
+      <c r="B142" s="17" t="inlineStr">
+        <is>
           <t>W9127826RA025</t>
         </is>
       </c>
-      <c r="C137" s="38" t="inlineStr">
+      <c r="C142" s="30" t="inlineStr">
         <is>
           <t>Phillips Parkway Haul Route</t>
         </is>
       </c>
-      <c r="D137" s="20" t="inlineStr">
+      <c r="D142" s="17" t="inlineStr">
         <is>
           <t>Cape Canaveral, Florida</t>
         </is>
       </c>
-      <c r="E137" s="20" t="inlineStr">
+      <c r="E142" s="17" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F137" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G137" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H137" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I137" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J137" s="20" t="inlineStr">
+      <c r="F142" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G142" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H142" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J142" s="17" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="K137" s="40" t="inlineStr">
+      <c r="K142" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K137"/>
+  <autoFilter ref="B5:K142"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -16867,6 +17451,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16879,7 +17468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K74"/>
+  <dimension ref="B2:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -16907,7 +17496,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="45" t="inlineStr">
         <is>
-          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  69 records  (14 SDVOSB)  ·  June 10, 2026</t>
+          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  71 records  (14 SDVOSB)  ·  June 10, 2026</t>
         </is>
       </c>
     </row>
@@ -18428,7 +19017,7 @@
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
+          <t>61--AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
@@ -18948,12 +19537,12 @@
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
+          <t>841st Network Cabling Installation</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Charleston, South Carolina</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
@@ -18968,12 +19557,12 @@
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>Jun 27, 2026</t>
+          <t>Jun 26, 2026</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>15d</t>
         </is>
       </c>
       <c r="I44" s="17" t="inlineStr">
@@ -18995,12 +19584,12 @@
     <row r="45" ht="28" customHeight="1">
       <c r="B45" s="52" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C45" s="53" t="inlineStr">
         <is>
-          <t>Denison Substation Stage 10, Iowa</t>
+          <t>CT SWITCHGEAR REPLACEMENT STAMPEDE PP</t>
         </is>
       </c>
       <c r="D45" s="54" t="inlineStr">
@@ -19020,12 +19609,12 @@
       </c>
       <c r="G45" s="54" t="inlineStr">
         <is>
-          <t>Jun 29, 2026</t>
+          <t>Jun 27, 2026</t>
         </is>
       </c>
       <c r="H45" s="54" t="inlineStr">
         <is>
-          <t>18d</t>
+          <t>16d</t>
         </is>
       </c>
       <c r="I45" s="54" t="inlineStr">
@@ -19052,7 +19641,7 @@
       </c>
       <c r="C46" s="30" t="inlineStr">
         <is>
-          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
+          <t>Denison Substation Stage 10, Iowa</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
@@ -19067,7 +19656,7 @@
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>$23.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
@@ -19099,12 +19688,12 @@
     <row r="47" ht="28" customHeight="1">
       <c r="B47" s="52" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C47" s="53" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
         </is>
       </c>
       <c r="D47" s="54" t="inlineStr">
@@ -19119,17 +19708,17 @@
       </c>
       <c r="F47" s="54" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="G47" s="54" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 29, 2026</t>
         </is>
       </c>
       <c r="H47" s="54" t="inlineStr">
         <is>
-          <t>19d</t>
+          <t>18d</t>
         </is>
       </c>
       <c r="I47" s="54" t="inlineStr">
@@ -19151,17 +19740,17 @@
     <row r="48" ht="28" customHeight="1">
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C48" s="30" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E48" s="17" t="inlineStr">
@@ -19171,7 +19760,7 @@
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
@@ -19203,17 +19792,17 @@
     <row r="49" ht="28" customHeight="1">
       <c r="B49" s="52" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C49" s="53" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="D49" s="54" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="E49" s="54" t="inlineStr">
@@ -19223,17 +19812,17 @@
       </c>
       <c r="F49" s="54" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G49" s="54" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="H49" s="54" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="I49" s="54" t="inlineStr">
@@ -19260,7 +19849,7 @@
       </c>
       <c r="C50" s="30" t="inlineStr">
         <is>
-          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -19275,17 +19864,17 @@
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="I50" s="17" t="inlineStr">
@@ -19307,12 +19896,12 @@
     <row r="51" ht="28" customHeight="1">
       <c r="B51" s="52" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C51" s="53" t="inlineStr">
         <is>
-          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
+          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
         </is>
       </c>
       <c r="D51" s="54" t="inlineStr">
@@ -19359,12 +19948,12 @@
     <row r="52" ht="28" customHeight="1">
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C52" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
+          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -19384,12 +19973,12 @@
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
@@ -19416,7 +20005,7 @@
       </c>
       <c r="C53" s="53" t="inlineStr">
         <is>
-          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
+          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
         </is>
       </c>
       <c r="D53" s="54" t="inlineStr">
@@ -19431,17 +20020,17 @@
       </c>
       <c r="F53" s="54" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G53" s="54" t="inlineStr">
         <is>
-          <t>Jul 10, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="H53" s="54" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>26d</t>
         </is>
       </c>
       <c r="I53" s="54" t="inlineStr">
@@ -19463,12 +20052,12 @@
     <row r="54" ht="28" customHeight="1">
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
+          <t>Base Operations Support Contract (BOSC) for Naval Air Weapons Station (NAWS) China Lake, California and Other Locations as Approved</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -19515,12 +20104,12 @@
     <row r="55" ht="28" customHeight="1">
       <c r="B55" s="52" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C55" s="53" t="inlineStr">
         <is>
-          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
+          <t>J--GC26 FIRE ALARM SYSTEM REPLACEMENT</t>
         </is>
       </c>
       <c r="D55" s="54" t="inlineStr">
@@ -19567,12 +20156,12 @@
     <row r="56" ht="28" customHeight="1">
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>237120 — Oil &amp; Gas Pipeline</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C56" s="30" t="inlineStr">
         <is>
-          <t>Solicitation for Grand Forks Fueling System Repairs</t>
+          <t>CHINA LAKE BOSC - SOLICITATION - N6247326R0053</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -19619,12 +20208,12 @@
     <row r="57" ht="28" customHeight="1">
       <c r="B57" s="52" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>237120 — Oil &amp; Gas Pipeline</t>
         </is>
       </c>
       <c r="C57" s="53" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Solicitation for Grand Forks Fueling System Repairs</t>
         </is>
       </c>
       <c r="D57" s="54" t="inlineStr">
@@ -19644,12 +20233,12 @@
       </c>
       <c r="G57" s="54" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="H57" s="54" t="inlineStr">
         <is>
-          <t>34d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="I57" s="54" t="inlineStr">
@@ -19657,9 +20246,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J57" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J57" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K57" s="55" t="inlineStr">
@@ -19671,17 +20260,17 @@
     <row r="58" ht="28" customHeight="1">
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>Marine Corps Base Camp Pendleton (MCBCP) Base Operations Support Contract (BOSC)</t>
+          <t>GAOA Grand Isle NRA Water System Improvement</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t>Oceanside, California</t>
+          <t>Munising, Michigan</t>
         </is>
       </c>
       <c r="E58" s="17" t="inlineStr">
@@ -19691,17 +20280,17 @@
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 10, 2026</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
@@ -19709,9 +20298,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J58" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J58" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K58" s="32" t="inlineStr">
@@ -19723,12 +20312,12 @@
     <row r="59" ht="28" customHeight="1">
       <c r="B59" s="52" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C59" s="53" t="inlineStr">
         <is>
-          <t>VA-HARRISON LAKE NFH-REPL ELECTRICAL VC</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D59" s="54" t="inlineStr">
@@ -19748,12 +20337,12 @@
       </c>
       <c r="G59" s="54" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H59" s="54" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>34d</t>
         </is>
       </c>
       <c r="I59" s="54" t="inlineStr">
@@ -19761,9 +20350,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J59" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J59" s="42" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K59" s="55" t="inlineStr">
@@ -19775,17 +20364,17 @@
     <row r="60" ht="28" customHeight="1">
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>Repair/Replace Traffic Lights</t>
+          <t>Marine Corps Base Camp Pendleton (MCBCP) Base Operations Support Contract (BOSC)</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>Little Rock Air Force Base, Arkansas</t>
+          <t>Oceanside, California</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
@@ -19795,7 +20384,7 @@
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
@@ -19832,12 +20421,12 @@
       </c>
       <c r="C61" s="53" t="inlineStr">
         <is>
-          <t>Z--WACO Emergency Generator</t>
+          <t>VA-HARRISON LAKE NFH-REPL ELECTRICAL VC</t>
         </is>
       </c>
       <c r="D61" s="54" t="inlineStr">
         <is>
-          <t>Waco, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E61" s="54" t="inlineStr">
@@ -19847,22 +20436,22 @@
       </c>
       <c r="F61" s="54" t="inlineStr">
         <is>
-          <t>$62K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G61" s="54" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="H61" s="54" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="I61" s="54" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="J61" s="18" t="inlineStr">
@@ -19884,12 +20473,12 @@
       </c>
       <c r="C62" s="30" t="inlineStr">
         <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
+          <t>Repair/Replace Traffic Lights</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Little Rock Air Force Base, Arkansas</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
@@ -19904,17 +20493,17 @@
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="J62" s="18" t="inlineStr">
@@ -19931,17 +20520,17 @@
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="52" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C63" s="53" t="inlineStr">
         <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
+          <t>Z--WACO Emergency Generator</t>
         </is>
       </c>
       <c r="D63" s="54" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Waco, Texas</t>
         </is>
       </c>
       <c r="E63" s="54" t="inlineStr">
@@ -19951,17 +20540,17 @@
       </c>
       <c r="F63" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="G63" s="54" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="H63" s="54" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="I63" s="54" t="inlineStr">
@@ -19983,17 +20572,17 @@
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
@@ -20003,7 +20592,7 @@
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
@@ -20035,17 +20624,17 @@
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="52" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C65" s="53" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D65" s="54" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E65" s="54" t="inlineStr">
@@ -20055,17 +20644,17 @@
       </c>
       <c r="F65" s="54" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G65" s="54" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="H65" s="54" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>11d</t>
         </is>
       </c>
       <c r="I65" s="54" t="inlineStr">
@@ -20087,17 +20676,17 @@
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C66" s="30" t="inlineStr">
         <is>
-          <t>Y--Beresford Substation Stage 11, South Dakota</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -20107,17 +20696,17 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>34d</t>
+          <t>11d</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
@@ -20125,9 +20714,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J66" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J66" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K66" s="32" t="inlineStr">
@@ -20139,17 +20728,17 @@
     <row r="67" ht="28" customHeight="1">
       <c r="B67" s="52" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C67" s="53" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="D67" s="54" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E67" s="54" t="inlineStr">
@@ -20159,17 +20748,17 @@
       </c>
       <c r="F67" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.1M</t>
         </is>
       </c>
       <c r="G67" s="54" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="H67" s="54" t="inlineStr">
         <is>
-          <t>34d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="I67" s="54" t="inlineStr">
@@ -20177,9 +20766,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J67" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J67" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K67" s="55" t="inlineStr">
@@ -20191,12 +20780,12 @@
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C68" s="30" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Y--Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
@@ -20216,12 +20805,12 @@
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>43d</t>
+          <t>34d</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
@@ -20243,17 +20832,17 @@
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="52" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C69" s="53" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D69" s="54" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E69" s="54" t="inlineStr">
@@ -20268,12 +20857,12 @@
       </c>
       <c r="G69" s="54" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H69" s="54" t="inlineStr">
         <is>
-          <t>43d</t>
+          <t>34d</t>
         </is>
       </c>
       <c r="I69" s="54" t="inlineStr">
@@ -20295,12 +20884,12 @@
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
@@ -20315,17 +20904,17 @@
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>78d</t>
+          <t>43d</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
@@ -20347,17 +20936,17 @@
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="52" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C71" s="53" t="inlineStr">
         <is>
-          <t>USAO Schwartz Conference Room Display Upgrade</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D71" s="54" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E71" s="54" t="inlineStr">
@@ -20372,12 +20961,12 @@
       </c>
       <c r="G71" s="54" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="H71" s="54" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>43d</t>
         </is>
       </c>
       <c r="I71" s="54" t="inlineStr">
@@ -20385,9 +20974,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J71" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J71" s="42" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K71" s="55" t="inlineStr">
@@ -20399,12 +20988,12 @@
     <row r="72" ht="28" customHeight="1">
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
@@ -20419,17 +21008,17 @@
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78d</t>
         </is>
       </c>
       <c r="I72" s="17" t="inlineStr">
@@ -20439,7 +21028,7 @@
       </c>
       <c r="J72" s="42" t="inlineStr">
         <is>
-          <t>Pre-Sol</t>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K72" s="32" t="inlineStr">
@@ -20451,17 +21040,17 @@
     <row r="73" ht="28" customHeight="1">
       <c r="B73" s="52" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C73" s="53" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>USAO Schwartz Conference Room Display Upgrade</t>
         </is>
       </c>
       <c r="D73" s="54" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>California</t>
         </is>
       </c>
       <c r="E73" s="54" t="inlineStr">
@@ -20471,17 +21060,17 @@
       </c>
       <c r="F73" s="54" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="H73" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="I73" s="54" t="inlineStr">
@@ -20489,9 +21078,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J73" s="42" t="inlineStr">
-        <is>
-          <t>Pre-Sol</t>
+      <c r="J73" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K73" s="55" t="inlineStr">
@@ -20503,57 +21092,161 @@
     <row r="74" ht="28" customHeight="1">
       <c r="B74" s="16" t="inlineStr">
         <is>
+          <t>237110 — Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J74" s="42" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="B75" s="52" t="inlineStr">
+        <is>
+          <t>237110 — Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="C75" s="53" t="inlineStr">
+        <is>
+          <t>Rosebud Lift Station Construction</t>
+        </is>
+      </c>
+      <c r="D75" s="54" t="inlineStr">
+        <is>
+          <t>Rosebud, South Dakota</t>
+        </is>
+      </c>
+      <c r="E75" s="54" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F75" s="54" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+      <c r="G75" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="54" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J75" s="42" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K75" s="55" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="B76" s="16" t="inlineStr">
+        <is>
           <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
-      <c r="C74" s="30" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E74" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="F74" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="17" t="inlineStr">
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="H74" s="17" t="inlineStr">
+      <c r="H76" s="17" t="inlineStr">
         <is>
           <t>19d</t>
         </is>
       </c>
-      <c r="I74" s="17" t="inlineStr">
+      <c r="I76" s="17" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="J74" s="41" t="inlineStr">
+      <c r="J76" s="41" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="K74" s="32" t="inlineStr">
+      <c r="K76" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K74"/>
+  <autoFilter ref="B5:K76"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -20628,6 +21321,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
